--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4735-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4735-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{758E84C3-28AE-4951-BA1D-4699C37EAAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4F373AA-0DDE-4E51-AE0C-6C17E3B55D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{42FFB97C-21C6-4C91-8193-9771F0FFF264}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{4DF6DFE5-DDA1-45B1-A36C-182BE36F87BD}"/>
   </bookViews>
   <sheets>
     <sheet name="4735-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1517,28 +1517,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3797F9F8-2594-4E5B-A6D9-F1EB7DA7E95B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B4DD0E-C1DC-42D6-95F7-81DDFD4EE8C0}">
   <dimension ref="A1:X44"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1572,7 +1572,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1608,7 +1608,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1728,7 +1728,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>28</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>28</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>28</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2024</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>28</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>28</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>28</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>28</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2023</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>28</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>28</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>28</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>28</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2022</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>28</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>28</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>28</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>28</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2021</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>28</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>28</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>28</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>28</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2020</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>28</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>5.67</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>28</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2019</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2018</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2017</v>
       </c>
@@ -3930,7 +3930,7 @@
         <v>8.24</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2016</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>2015</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2014</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>2013</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2012</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>2011</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>2010</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>2009</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>2008</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35" t="s">
         <v>60</v>
       </c>
